--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -11645,6 +11645,154 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11678,7 +11826,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11909,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -11771,7 +11919,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2387,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2532,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3873,9 +3861,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4021,9 +4006,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -5353,9 +5335,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5501,9 +5480,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6833,9 +6809,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -6981,9 +6954,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8609,9 +8579,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -8757,9 +8724,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -8905,9 +8869,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +9014,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9201,9 +9159,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9349,9 +9304,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -9497,9 +9449,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9645,9 +9594,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9739,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -9941,9 +9884,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10089,9 +10029,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10237,9 +10174,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -10385,9 +10319,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10533,9 +10464,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10609,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -10829,9 +10754,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -10977,9 +10899,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11125,9 +11044,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11273,9 +11189,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11334,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -11569,9 +11479,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -11715,9 +11622,6 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -11697,6 +11697,151 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11730,7 +11875,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11958,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -11823,7 +11968,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -11842,6 +11842,151 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11875,7 +12020,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11958,7 +12103,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -11968,7 +12113,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -20229,12 +20229,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20307,42 +20307,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20374,12 +20374,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20404,7 +20404,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -20452,42 +20452,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20519,12 +20519,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20597,42 +20597,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20664,12 +20664,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -20708,9 +20708,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -20719,77 +20716,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20816,7 +20804,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -20868,98 +20856,18 @@
       <c r="P121" t="n">
         <v>0</v>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -21053,17 +20961,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21088,7 +20996,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -21102,76 +21010,168 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21203,12 +21203,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21281,42 +21281,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21348,12 +21348,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21378,7 +21378,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21392,9 +21392,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -21403,77 +21400,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21500,7 +21488,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -21552,98 +21540,18 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -21737,17 +21645,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21772,7 +21680,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21786,76 +21694,168 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -21887,12 +21887,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21965,42 +21965,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22032,12 +22032,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22062,7 +22062,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22076,9 +22076,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22087,77 +22084,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22172,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -22236,98 +22224,18 @@
       <c r="P129" t="n">
         <v>0</v>
       </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>1</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -22421,17 +22329,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22456,7 +22364,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22470,76 +22378,168 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -22571,12 +22571,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22649,42 +22649,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22716,12 +22716,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22794,42 +22794,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22861,12 +22861,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22905,9 +22905,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -22916,77 +22913,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23013,7 +23001,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -23065,98 +23053,18 @@
       <c r="P134" t="n">
         <v>0</v>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V134" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD134" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG134" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN134" t="b">
-        <v>1</v>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
@@ -23250,17 +23158,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23285,12 +23193,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -23299,76 +23207,168 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -23400,12 +23400,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23430,7 +23430,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -23478,42 +23478,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23545,12 +23545,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23589,9 +23589,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="P137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -23600,77 +23597,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23685,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -23749,98 +23737,18 @@
       <c r="P138" t="n">
         <v>0</v>
       </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -23934,17 +23842,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23969,7 +23877,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -23983,76 +23891,168 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24084,12 +24084,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24128,9 +24128,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -24139,77 +24136,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24236,7 +24224,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -24288,98 +24276,18 @@
       <c r="P141" t="n">
         <v>0</v>
       </c>
-      <c r="U141" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -24473,17 +24381,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24508,7 +24416,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24522,76 +24430,168 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -24623,12 +24623,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24667,9 +24667,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -24678,77 +24675,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24775,7 +24763,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -24827,98 +24815,18 @@
       <c r="P144" t="n">
         <v>0</v>
       </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_YELLOW_FEVER</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Yellow Fever</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -24984,6 +24892,243 @@
         </is>
       </c>
       <c r="BC144" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -25105,7 +25250,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -25115,7 +25260,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d059/2026-2029.xlsx
+++ b/diseases/d059/2026-2029.xlsx
@@ -25134,6 +25134,690 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Yellow Fever</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_YELLOW_FEVER; SER_SG_HIST_YELLOW_FEVER</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25167,7 +25851,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -25250,7 +25934,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -25260,7 +25944,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -25280,7 +25964,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
